--- a/시간 기록.xlsx
+++ b/시간 기록.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smart\Documents\가톨릭대학교\자유주제연구\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF3E238-B4C4-4A3D-B31B-03D36F2CB004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9C7BA9-7140-4659-ADCF-9962C09784EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="770" yWindow="940" windowWidth="16940" windowHeight="9620" xr2:uid="{0EA546E3-6824-4D5F-BF37-598D3A4BAFC2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0EA546E3-6824-4D5F-BF37-598D3A4BAFC2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -528,7 +531,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -568,95 +571,92 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -674,6 +674,189 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>150091</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>92363</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>295505</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>16005</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C448191F-1465-257D-9AB9-F17487260DF0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8047182" y="3821545"/>
+          <a:ext cx="7846232" cy="5627096"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="B2">
+            <v>0.2</v>
+          </cell>
+          <cell r="C2">
+            <v>0.16</v>
+          </cell>
+          <cell r="D2">
+            <v>0.1</v>
+          </cell>
+          <cell r="E2">
+            <v>0.08</v>
+          </cell>
+          <cell r="F2">
+            <v>0.05</v>
+          </cell>
+          <cell r="G2">
+            <v>0.04</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>10</v>
+          </cell>
+          <cell r="B3">
+            <v>0.746</v>
+          </cell>
+          <cell r="C3">
+            <v>1.74925</v>
+          </cell>
+          <cell r="D3">
+            <v>9.90625</v>
+          </cell>
+          <cell r="E3">
+            <v>23.614249999999998</v>
+          </cell>
+          <cell r="F3">
+            <v>137.74475000000001</v>
+          </cell>
+          <cell r="G3">
+            <v>322.41325000000001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>14</v>
+          </cell>
+          <cell r="G4">
+            <v>374.67875000000004</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>15</v>
+          </cell>
+          <cell r="B5">
+            <v>1.01725</v>
+          </cell>
+          <cell r="C5">
+            <v>2.1440000000000001</v>
+          </cell>
+          <cell r="D5">
+            <v>10.86525</v>
+          </cell>
+          <cell r="E5">
+            <v>27.564</v>
+          </cell>
+          <cell r="F5">
+            <v>163.47199999999998</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>17</v>
+          </cell>
+          <cell r="F6">
+            <v>182.43700000000001</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>18</v>
+          </cell>
+          <cell r="B7">
+            <v>1.4345000000000001</v>
+          </cell>
+          <cell r="C7">
+            <v>3.0225</v>
+          </cell>
+          <cell r="D7">
+            <v>12.19875</v>
+          </cell>
+          <cell r="E7">
+            <v>32.628999999999998</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>21</v>
+          </cell>
+          <cell r="C9">
+            <v>3.2345000000000002</v>
+          </cell>
+          <cell r="D9">
+            <v>16.049500000000002</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>22</v>
+          </cell>
+          <cell r="E10">
+            <v>37.536749999999998</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -986,54 +1169,54 @@
     <row r="2" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="29">
+      <c r="D3" s="25">
         <v>0.2</v>
       </c>
-      <c r="E3" s="30"/>
-      <c r="F3" s="31">
+      <c r="E3" s="24"/>
+      <c r="F3" s="23">
         <v>0.16</v>
       </c>
-      <c r="G3" s="30"/>
-      <c r="H3" s="31">
+      <c r="G3" s="24"/>
+      <c r="H3" s="23">
         <v>0.1</v>
       </c>
-      <c r="I3" s="30"/>
-      <c r="J3" s="31">
+      <c r="I3" s="24"/>
+      <c r="J3" s="23">
         <v>0.08</v>
       </c>
-      <c r="K3" s="30"/>
-      <c r="L3" s="31">
+      <c r="K3" s="24"/>
+      <c r="L3" s="23">
         <v>0.05</v>
       </c>
-      <c r="M3" s="30"/>
-      <c r="N3" s="31">
+      <c r="M3" s="24"/>
+      <c r="N3" s="23">
         <v>0.04</v>
       </c>
-      <c r="O3" s="30"/>
+      <c r="O3" s="24"/>
     </row>
     <row r="4" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="22">
+      <c r="C4" s="26">
         <v>10</v>
       </c>
       <c r="D4" s="8">
@@ -1074,8 +1257,8 @@
       </c>
     </row>
     <row r="5" spans="2:20" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="13"/>
-      <c r="C5" s="23"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="27"/>
       <c r="D5" s="8">
         <v>0.75</v>
       </c>
@@ -1118,48 +1301,47 @@
       <c r="T5" s="7"/>
     </row>
     <row r="6" spans="2:20" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B6" s="13"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="19">
+      <c r="B6" s="22"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="39">
         <f>AVERAGE(D4:E5)</f>
         <v>0.746</v>
       </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="19">
+      <c r="E6" s="40"/>
+      <c r="F6" s="39">
         <f t="shared" ref="F6" si="0">AVERAGE(F4:G5)</f>
         <v>1.74925</v>
       </c>
-      <c r="G6" s="18"/>
-      <c r="H6" s="19">
+      <c r="G6" s="40"/>
+      <c r="H6" s="39">
         <f t="shared" ref="H6" si="1">AVERAGE(H4:I5)</f>
         <v>9.90625</v>
       </c>
-      <c r="I6" s="18"/>
-      <c r="J6" s="19">
+      <c r="I6" s="40"/>
+      <c r="J6" s="39">
         <f t="shared" ref="J6" si="2">AVERAGE(J4:K5)</f>
         <v>23.614249999999998</v>
       </c>
-      <c r="K6" s="18"/>
-      <c r="L6" s="19">
+      <c r="K6" s="40"/>
+      <c r="L6" s="39">
         <f t="shared" ref="L6" si="3">AVERAGE(L4:M5)</f>
         <v>137.74475000000001</v>
       </c>
-      <c r="M6" s="18"/>
-      <c r="N6" s="19">
+      <c r="M6" s="40"/>
+      <c r="N6" s="39">
         <f t="shared" ref="N6" si="4">AVERAGE(N4:O5)</f>
         <v>322.41325000000001</v>
       </c>
-      <c r="O6" s="18"/>
+      <c r="O6" s="40"/>
       <c r="Q6" s="8"/>
-      <c r="R6" s="25"/>
-      <c r="S6" s="25" t="s">
+      <c r="S6" t="s">
         <v>4</v>
       </c>
       <c r="T6" s="9"/>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B7" s="13"/>
-      <c r="C7" s="14">
+      <c r="B7" s="22"/>
+      <c r="C7" s="21">
         <v>15</v>
       </c>
       <c r="D7" s="8">
@@ -1192,20 +1374,18 @@
       <c r="M7" s="9">
         <v>160.05500000000001</v>
       </c>
-      <c r="N7" s="36" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="41" t="s">
+      <c r="N7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O7" s="19" t="s">
         <v>5</v>
       </c>
       <c r="Q7" s="8"/>
-      <c r="R7" s="25"/>
-      <c r="S7" s="25"/>
       <c r="T7" s="9"/>
     </row>
     <row r="8" spans="2:20" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="13"/>
-      <c r="C8" s="14"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="21"/>
       <c r="D8" s="8">
         <v>0.96799999999999997</v>
       </c>
@@ -1236,67 +1416,65 @@
       <c r="M8" s="9">
         <v>168.84399999999999</v>
       </c>
-      <c r="N8" s="36" t="s">
-        <v>5</v>
-      </c>
-      <c r="O8" s="41" t="s">
+      <c r="N8" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O8" s="19" t="s">
         <v>5</v>
       </c>
       <c r="Q8" s="8"/>
-      <c r="R8" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="S8" s="25" t="s">
+      <c r="R8" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="S8" t="s">
         <v>6</v>
       </c>
       <c r="T8" s="9"/>
     </row>
     <row r="9" spans="2:20" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="15">
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="34">
         <f>AVERAGE(D7:E8)</f>
         <v>1.01725</v>
       </c>
-      <c r="E9" s="16"/>
-      <c r="F9" s="15">
+      <c r="E9" s="38"/>
+      <c r="F9" s="34">
         <f t="shared" ref="F9" si="5">AVERAGE(F7:G8)</f>
         <v>2.1440000000000001</v>
       </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="15">
+      <c r="G9" s="38"/>
+      <c r="H9" s="34">
         <f t="shared" ref="H9" si="6">AVERAGE(H7:I8)</f>
         <v>10.86525</v>
       </c>
-      <c r="I9" s="16"/>
-      <c r="J9" s="15">
+      <c r="I9" s="38"/>
+      <c r="J9" s="34">
         <f t="shared" ref="J9" si="7">AVERAGE(J7:K8)</f>
         <v>27.564</v>
       </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="15">
+      <c r="K9" s="38"/>
+      <c r="L9" s="34">
         <f t="shared" ref="L9" si="8">AVERAGE(L7:M8)</f>
         <v>163.47199999999998</v>
       </c>
-      <c r="M9" s="32"/>
-      <c r="N9" s="35" t="s">
-        <v>5</v>
-      </c>
-      <c r="O9" s="17"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="33"/>
       <c r="Q9" s="8"/>
-      <c r="R9" s="25"/>
-      <c r="S9" s="25"/>
       <c r="T9" s="9"/>
     </row>
     <row r="10" spans="2:20" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B10" s="13"/>
-      <c r="C10" s="14">
+      <c r="B10" s="22"/>
+      <c r="C10" s="21">
         <v>20</v>
       </c>
-      <c r="D10" s="40" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="41" t="s">
+      <c r="D10" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="19" t="s">
         <v>5</v>
       </c>
       <c r="F10">
@@ -1317,42 +1495,42 @@
       <c r="K10" s="9">
         <v>29.686</v>
       </c>
-      <c r="L10" s="36" t="s">
-        <v>5</v>
-      </c>
-      <c r="M10" s="41" t="s">
-        <v>5</v>
-      </c>
-      <c r="N10" s="36" t="s">
-        <v>5</v>
-      </c>
-      <c r="O10" s="41" t="s">
+      <c r="L10" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="M10" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="19" t="s">
         <v>5</v>
       </c>
       <c r="Q10" s="8"/>
       <c r="R10" s="2"/>
-      <c r="S10" s="25" t="s">
+      <c r="S10" t="s">
         <v>3</v>
       </c>
       <c r="T10" s="9"/>
     </row>
     <row r="11" spans="2:20" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="13"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="40" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="41" t="s">
+      <c r="B11" s="22"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="19" t="s">
         <v>5</v>
       </c>
       <c r="F11">
         <v>2.9020000000000001</v>
       </c>
-      <c r="G11" s="9">
-        <v>2.734</v>
+      <c r="G11">
+        <v>2.9020000000000001</v>
       </c>
       <c r="H11">
-        <v>14.257</v>
+        <v>2.9020000000000001</v>
       </c>
       <c r="I11" s="9">
         <v>15.497</v>
@@ -1363,63 +1541,61 @@
       <c r="K11" s="9">
         <v>34.377000000000002</v>
       </c>
-      <c r="L11" s="36" t="s">
-        <v>5</v>
-      </c>
-      <c r="M11" s="41" t="s">
-        <v>5</v>
-      </c>
-      <c r="N11" s="36" t="s">
-        <v>5</v>
-      </c>
-      <c r="O11" s="41" t="s">
+      <c r="L11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="N11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="O11" s="19" t="s">
         <v>5</v>
       </c>
       <c r="Q11" s="8"/>
-      <c r="R11" s="25"/>
-      <c r="S11" s="25"/>
       <c r="T11" s="9"/>
     </row>
     <row r="12" spans="2:20" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B12" s="13"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="33"/>
-      <c r="F12" s="15">
+      <c r="B12" s="22"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="37"/>
+      <c r="F12" s="34">
         <f>AVERAGE(F10:G11)</f>
-        <v>2.9804999999999997</v>
-      </c>
-      <c r="G12" s="34"/>
-      <c r="H12" s="15">
+        <v>3.0225</v>
+      </c>
+      <c r="G12" s="41"/>
+      <c r="H12" s="34">
         <f t="shared" ref="H12" si="9">AVERAGE(H10:I11)</f>
-        <v>15.0375</v>
-      </c>
-      <c r="I12" s="34"/>
-      <c r="J12" s="15">
+        <v>12.19875</v>
+      </c>
+      <c r="I12" s="41"/>
+      <c r="J12" s="34">
         <f t="shared" ref="J12" si="10">AVERAGE(J10:K11)</f>
         <v>32.628999999999998</v>
       </c>
-      <c r="K12" s="34"/>
-      <c r="L12" s="35" t="s">
-        <v>5</v>
-      </c>
-      <c r="M12" s="17"/>
-      <c r="N12" s="35" t="s">
-        <v>5</v>
-      </c>
-      <c r="O12" s="17"/>
+      <c r="K12" s="41"/>
+      <c r="L12" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="M12" s="33"/>
+      <c r="N12" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="O12" s="33"/>
       <c r="Q12" s="8"/>
-      <c r="R12" s="28"/>
-      <c r="S12" s="25" t="s">
+      <c r="R12" s="15"/>
+      <c r="S12" t="s">
         <v>2</v>
       </c>
       <c r="T12" s="9"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B13" s="13"/>
-      <c r="C13" s="21" t="s">
+      <c r="B13" s="22"/>
+      <c r="C13" s="29" t="s">
         <v>0</v>
       </c>
       <c r="D13" s="8">
@@ -1459,46 +1635,45 @@
         <v>372.346</v>
       </c>
       <c r="Q13" s="8"/>
-      <c r="R13" s="25"/>
-      <c r="S13" s="25" t="s">
+      <c r="S13" t="s">
         <v>8</v>
       </c>
       <c r="T13" s="9"/>
     </row>
     <row r="14" spans="2:20" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B14" s="13"/>
-      <c r="C14" s="38"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="30"/>
       <c r="D14" s="8">
         <v>1.5920000000000001</v>
       </c>
       <c r="E14" s="9">
         <v>1.22</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14">
         <v>2.99</v>
       </c>
       <c r="G14" s="9">
         <v>3.0350000000000001</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14">
         <v>17.370999999999999</v>
       </c>
       <c r="I14" s="9">
         <v>17.056999999999999</v>
       </c>
-      <c r="J14" s="25">
+      <c r="J14">
         <v>37.938000000000002</v>
       </c>
       <c r="K14" s="9">
         <v>40.933999999999997</v>
       </c>
-      <c r="L14" s="25">
+      <c r="L14">
         <v>191.24799999999999</v>
       </c>
       <c r="M14" s="9">
         <v>190.82400000000001</v>
       </c>
-      <c r="N14" s="25">
+      <c r="N14">
         <v>376.54399999999998</v>
       </c>
       <c r="O14" s="9">
@@ -1507,47 +1682,47 @@
       <c r="Q14" s="3"/>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
-      <c r="T14" s="42"/>
+      <c r="T14" s="20"/>
     </row>
     <row r="15" spans="2:20" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="13"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="27">
+      <c r="B15" s="22"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="14">
         <v>18</v>
       </c>
       <c r="E15" s="12">
         <f>AVERAGE(D13:E14)</f>
         <v>1.4345000000000001</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="13">
         <v>21</v>
       </c>
       <c r="G15" s="12">
         <f>AVERAGE(F13:G14)</f>
         <v>3.2345000000000002</v>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="13">
         <v>21</v>
       </c>
       <c r="I15" s="12">
         <f>AVERAGE(H13:I14)</f>
         <v>16.049500000000002</v>
       </c>
-      <c r="J15" s="26">
+      <c r="J15" s="13">
         <v>22</v>
       </c>
       <c r="K15" s="12">
         <f>AVERAGE(J13:K14)</f>
         <v>37.536749999999998</v>
       </c>
-      <c r="L15" s="26">
+      <c r="L15" s="13">
         <v>17</v>
       </c>
       <c r="M15" s="12">
         <f>AVERAGE(L13:M14)</f>
         <v>182.43700000000001</v>
       </c>
-      <c r="N15" s="26">
+      <c r="N15" s="13">
         <v>14</v>
       </c>
       <c r="O15" s="12">
@@ -1557,11 +1732,18 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="B4:B15"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="H6:I6"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="N9:O9"/>
     <mergeCell ref="L9:M9"/>
@@ -1575,20 +1757,14 @@
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="H3:I3"/>
-    <mergeCell ref="B4:B15"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="C4:C6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>